--- a/data/18S/metadata_18S.xlsx
+++ b/data/18S/metadata_18S.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\Documents\GitHub\Augmentum_eDNA_metabarcoding\data\18S\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C144EFB1-DC29-4BA9-9A26-0BD584757C78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C072C04-22C0-475C-8FC1-3BFE74295147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-9525" windowWidth="29040" windowHeight="15720" xr2:uid="{A98CF8EC-D2DA-4B38-910A-EF3A2677D223}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A98CF8EC-D2DA-4B38-910A-EF3A2677D223}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="123">
   <si>
     <t>01_St1_D1</t>
   </si>
@@ -421,9 +421,6 @@
   </si>
   <si>
     <t>Iterdalk</t>
-  </si>
-  <si>
-    <t>Ocean</t>
   </si>
   <si>
     <t>Tunulliarfik</t>
@@ -1448,7 +1445,7 @@
         <v>88</v>
       </c>
       <c r="I20" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
@@ -1480,7 +1477,7 @@
         <v>88</v>
       </c>
       <c r="I21" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
@@ -1512,7 +1509,7 @@
         <v>88</v>
       </c>
       <c r="I22" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
@@ -1544,7 +1541,7 @@
         <v>90</v>
       </c>
       <c r="I23" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
@@ -1576,7 +1573,7 @@
         <v>90</v>
       </c>
       <c r="I24" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
@@ -1608,7 +1605,7 @@
         <v>90</v>
       </c>
       <c r="I25" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
@@ -2152,7 +2149,7 @@
         <v>104</v>
       </c>
       <c r="I42" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
@@ -2184,7 +2181,7 @@
         <v>104</v>
       </c>
       <c r="I43" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
@@ -2216,7 +2213,7 @@
         <v>104</v>
       </c>
       <c r="I44" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
@@ -2248,7 +2245,7 @@
         <v>106</v>
       </c>
       <c r="I45" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
@@ -2280,7 +2277,7 @@
         <v>106</v>
       </c>
       <c r="I46" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
@@ -2312,7 +2309,7 @@
         <v>106</v>
       </c>
       <c r="I47" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
@@ -2344,7 +2341,7 @@
         <v>108</v>
       </c>
       <c r="I48" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
@@ -2376,7 +2373,7 @@
         <v>108</v>
       </c>
       <c r="I49" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
@@ -2408,7 +2405,7 @@
         <v>108</v>
       </c>
       <c r="I50" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
@@ -2440,7 +2437,7 @@
         <v>110</v>
       </c>
       <c r="I51" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
@@ -2472,7 +2469,7 @@
         <v>110</v>
       </c>
       <c r="I52" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
@@ -2504,7 +2501,7 @@
         <v>110</v>
       </c>
       <c r="I53" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
@@ -2536,7 +2533,7 @@
         <v>112</v>
       </c>
       <c r="I54" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
@@ -2568,7 +2565,7 @@
         <v>112</v>
       </c>
       <c r="I55" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
@@ -2600,7 +2597,7 @@
         <v>112</v>
       </c>
       <c r="I56" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
@@ -2632,7 +2629,7 @@
         <v>114</v>
       </c>
       <c r="I57" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
@@ -2664,7 +2661,7 @@
         <v>114</v>
       </c>
       <c r="I58" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
@@ -2696,7 +2693,7 @@
         <v>114</v>
       </c>
       <c r="I59" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
@@ -2728,7 +2725,7 @@
         <v>116</v>
       </c>
       <c r="I60" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
@@ -2760,7 +2757,7 @@
         <v>116</v>
       </c>
       <c r="I61" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
@@ -2792,7 +2789,7 @@
         <v>116</v>
       </c>
       <c r="I62" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
@@ -2824,7 +2821,7 @@
         <v>118</v>
       </c>
       <c r="I63" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
@@ -2856,7 +2853,7 @@
         <v>118</v>
       </c>
       <c r="I64" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
@@ -2888,12 +2885,12 @@
         <v>118</v>
       </c>
       <c r="I65" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B66" t="str" cm="1">
         <f t="array" ref="B66">INDEX(_xlfn.TEXTSPLIT(A66,"_"),1)</f>
